--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run2/epoch_90/per_file_predictions_epoch_90.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run2/epoch_90/per_file_predictions_epoch_90.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="497">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="496">
   <si>
     <t>Filename</t>
   </si>
@@ -808,703 +808,700 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.9844,0.0037,0.0008,0.0017</t>
-  </si>
-  <si>
-    <t>0.0017,0.0000,0.0000,0.9996</t>
-  </si>
-  <si>
-    <t>0.9786,0.0006,0.0006,0.0127</t>
-  </si>
-  <si>
-    <t>0.1033,0.0007,0.0005,0.9556</t>
-  </si>
-  <si>
-    <t>0.9994,0.0004,0.0000,0.0000</t>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>0.9610,0.0063,0.0089,0.0040</t>
+  </si>
+  <si>
+    <t>0.0205,0.0000,0.0000,0.9973</t>
+  </si>
+  <si>
+    <t>0.9899,0.0006,0.0000,0.0023</t>
+  </si>
+  <si>
+    <t>0.0156,0.0080,0.0092,0.9837</t>
+  </si>
+  <si>
+    <t>0.9997,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9998,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>1.0000,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9992,0.0014,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9959,0.0049,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9929,0.0005,0.0020,0.0001</t>
+  </si>
+  <si>
+    <t>0.0614,0.0009,0.9428,0.0002</t>
+  </si>
+  <si>
+    <t>0.8251,0.0005,0.2423,0.0000</t>
+  </si>
+  <si>
+    <t>0.0015,0.0022,0.9970,0.0001</t>
+  </si>
+  <si>
+    <t>0.9749,0.0002,0.0268,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9997,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.0028,0.9966,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.0005,0.9991,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0951,0.0008,0.9094,0.0003</t>
+  </si>
+  <si>
+    <t>0.9323,0.0002,0.1093,0.0003</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.9997,0.0000</t>
+  </si>
+  <si>
+    <t>0.0066,0.0006,0.9920,0.0001</t>
+  </si>
+  <si>
+    <t>0.0038,0.0002,0.9957,0.0001</t>
+  </si>
+  <si>
+    <t>0.0060,0.0000,0.9940,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.9997,0.0003</t>
+  </si>
+  <si>
+    <t>0.2465,0.8614,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.6050,0.1306,0.0286,0.0016</t>
+  </si>
+  <si>
+    <t>0.0000,0.0012,0.9999,0.0068</t>
+  </si>
+  <si>
+    <t>0.0019,0.9892,0.0146,0.0001</t>
+  </si>
+  <si>
+    <t>0.9967,0.0011,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.0042,0.0027,0.9902,0.0035</t>
+  </si>
+  <si>
+    <t>0.1891,0.8185,0.0068,0.0001</t>
+  </si>
+  <si>
+    <t>0.0079,0.9800,0.0187,0.0002</t>
+  </si>
+  <si>
+    <t>0.0057,0.0034,0.9754,0.0010</t>
+  </si>
+  <si>
+    <t>0.0007,0.0666,0.9965,0.0020</t>
+  </si>
+  <si>
+    <t>0.0309,0.0112,0.9423,0.0002</t>
+  </si>
+  <si>
+    <t>0.0397,0.0000,0.9663,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0065,0.9994,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9997,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.0010,0.0001,0.9983,0.0001</t>
+  </si>
+  <si>
+    <t>0.0016,0.9769,0.0012,0.1243</t>
+  </si>
+  <si>
+    <t>0.0001,0.9998,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9991,0.0008,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0002,0.9994,0.0002</t>
+  </si>
+  <si>
+    <t>0.0002,0.0459,0.9991,0.0000</t>
+  </si>
+  <si>
+    <t>0.0510,0.0001,0.9665,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.0000,0.9995,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.0013,0.9982,0.0005</t>
+  </si>
+  <si>
+    <t>0.9942,0.0085,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9990,0.0002,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9979,0.0007,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.0010,0.0004,0.9989,0.0013</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9982,0.0009,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9979,0.0010,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9708,0.9513,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0038,0.9999,0.0001</t>
+  </si>
+  <si>
+    <t>0.0014,0.0003,0.9972,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9945,0.9911,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.9988,0.0026,0.0001</t>
+  </si>
+  <si>
+    <t>0.9926,0.0002,0.0057,0.0000</t>
+  </si>
+  <si>
+    <t>0.0547,0.0059,0.8946,0.0240</t>
+  </si>
+  <si>
+    <t>0.0002,0.0026,0.9996,0.0068</t>
+  </si>
+  <si>
+    <t>0.0000,0.9746,0.9969,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9262,0.9879,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0009,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9959,0.6589,0.0000</t>
+  </si>
+  <si>
+    <t>0.0167,0.0000,0.0006,0.9926</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0003,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.0005,0.0010,0.9993</t>
+  </si>
+  <si>
+    <t>0.0001,0.0006,0.0007,0.9996</t>
+  </si>
+  <si>
+    <t>0.0000,0.0012,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9982,0.8111,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.8460,0.9988,0.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.9288,0.7535,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9980,0.4917,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9980,0.9274,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.9798,0.4642,0.0001</t>
+  </si>
+  <si>
+    <t>0.9976,0.0024,0.0001,0.0000</t>
   </si>
   <si>
     <t>0.9990,0.0009,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9991,0.0007,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>1.0000,0.0000,0.0000,0.0000</t>
+    <t>0.9946,0.0086,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9990,0.0003,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9994,0.0006,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9990,0.0005,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9954,0.0031,0.0005,0.0002</t>
+  </si>
+  <si>
+    <t>0.9977,0.0027,0.0001,0.0000</t>
   </si>
   <si>
     <t>0.9999,0.0001,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9992,0.0009,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9997,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9970,0.0001,0.0013,0.0001</t>
-  </si>
-  <si>
-    <t>0.2414,0.0003,0.8069,0.0002</t>
-  </si>
-  <si>
-    <t>0.0969,0.0102,0.8563,0.0000</t>
-  </si>
-  <si>
-    <t>0.0022,0.0002,0.9972,0.0001</t>
-  </si>
-  <si>
-    <t>0.9686,0.0001,0.0525,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9996,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.0013,0.9976,0.0005,0.0002</t>
-  </si>
-  <si>
-    <t>0.0002,0.9995,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.6896,0.0001,0.4191,0.0002</t>
-  </si>
-  <si>
-    <t>0.9533,0.0001,0.0690,0.0003</t>
-  </si>
-  <si>
-    <t>0.0012,0.0000,0.9984,0.0000</t>
-  </si>
-  <si>
-    <t>0.0022,0.0002,0.9967,0.0001</t>
-  </si>
-  <si>
-    <t>0.0105,0.0000,0.9949,0.0000</t>
-  </si>
-  <si>
-    <t>0.0036,0.0000,0.9959,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.0001,0.9993,0.0003</t>
-  </si>
-  <si>
-    <t>0.3815,0.7821,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9960,0.0014,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0025,0.9998,0.0085</t>
-  </si>
-  <si>
-    <t>0.0031,0.9361,0.1257,0.0000</t>
-  </si>
-  <si>
-    <t>0.9968,0.0016,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.0372,0.0304,0.7954,0.0077</t>
-  </si>
-  <si>
-    <t>0.8718,0.1487,0.0022,0.0001</t>
-  </si>
-  <si>
-    <t>0.0024,0.9922,0.0199,0.0002</t>
-  </si>
-  <si>
-    <t>0.0018,0.0015,0.9942,0.0003</t>
-  </si>
-  <si>
-    <t>0.0032,0.0007,0.9937,0.0007</t>
-  </si>
-  <si>
-    <t>0.0140,0.0386,0.9512,0.0003</t>
-  </si>
-  <si>
-    <t>0.0004,0.0000,0.9995,0.0000</t>
-  </si>
-  <si>
-    <t>0.0025,0.0044,0.9954,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0007,0.0004,0.9988,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.9965,0.0009,0.0575</t>
-  </si>
-  <si>
-    <t>0.0001,0.9998,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.9999,0.0001</t>
-  </si>
-  <si>
-    <t>0.0005,0.0009,0.9992,0.0000</t>
-  </si>
-  <si>
-    <t>0.0068,0.0001,0.9929,0.0001</t>
-  </si>
-  <si>
-    <t>0.0029,0.0000,0.9975,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0008,0.0010,0.9979,0.0002</t>
-  </si>
-  <si>
-    <t>0.9946,0.0068,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9993,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9977,0.0011,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0004,0.9999,0.0010</t>
-  </si>
-  <si>
-    <t>0.9974,0.0010,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.9973,0.0010,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.9977,0.0009,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9972,0.6724,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0057,0.9999,0.0001</t>
-  </si>
-  <si>
-    <t>0.0005,0.0000,0.9994,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9938,0.9916,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,1.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.9994,0.0008,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9666,0.0009,0.0292,0.0002</t>
-  </si>
-  <si>
-    <t>0.6054,0.0147,0.1790,0.0010</t>
-  </si>
-  <si>
-    <t>0.0003,0.0009,0.9993,0.0029</t>
-  </si>
-  <si>
-    <t>0.0001,0.9592,0.9638,0.0000</t>
-  </si>
-  <si>
-    <t>0.0015,0.9536,0.3252,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0350,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9971,0.9882,0.0000</t>
-  </si>
-  <si>
-    <t>0.0033,0.0001,0.0034,0.9964</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.0001,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.0002,0.0004,0.0002,0.9998</t>
-  </si>
-  <si>
-    <t>0.0014,0.0000,0.0348,0.9932</t>
-  </si>
-  <si>
-    <t>0.0000,0.0010,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9952,0.9683,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9927,0.9983,0.0000</t>
-  </si>
-  <si>
-    <t>0.0012,0.9062,0.6621,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9857,0.9648,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9983,0.9912,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9918,0.7866,0.0000</t>
+    <t>0.9993,0.0009,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9997,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0002,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0014,0.0043,0.9965,0.0004</t>
+  </si>
+  <si>
+    <t>0.9986,0.0000,0.0006,0.0000</t>
+  </si>
+  <si>
+    <t>0.0008,0.0001,0.9991,0.0000</t>
+  </si>
+  <si>
+    <t>0.0008,0.9987,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0047,0.9923,0.0005,0.0007</t>
+  </si>
+  <si>
+    <t>0.0011,0.9973,0.0007,0.0003</t>
+  </si>
+  <si>
+    <t>0.0002,0.9996,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.4386,0.5999,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.0967,0.0035,0.8805,0.0006</t>
+  </si>
+  <si>
+    <t>0.9959,0.0000,0.0038,0.0000</t>
+  </si>
+  <si>
+    <t>0.9095,0.0234,0.0160,0.0004</t>
+  </si>
+  <si>
+    <t>0.8841,0.0040,0.0648,0.0015</t>
+  </si>
+  <si>
+    <t>0.0004,0.0012,0.0001,0.9991</t>
+  </si>
+  <si>
+    <t>0.0000,0.9998,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9947,0.9695,0.0000</t>
+  </si>
+  <si>
+    <t>0.0009,0.9989,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.9348,0.0480,0.0051,0.0002</t>
+  </si>
+  <si>
+    <t>0.8793,0.1121,0.0045,0.0001</t>
   </si>
   <si>
     <t>0.9999,0.0000,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9990,0.0010,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9987,0.0013,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9993,0.0006,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9995,0.0003,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9961,0.0025,0.0004,0.0002</t>
-  </si>
-  <si>
-    <t>0.9990,0.0011,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9998,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9994,0.0003,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9913,0.0116,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.9990,0.0005,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.0002,0.9997,0.0002</t>
-  </si>
-  <si>
-    <t>0.0015,0.0032,0.9968,0.0002</t>
-  </si>
-  <si>
-    <t>0.9994,0.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0109,0.0000,0.9921,0.0000</t>
-  </si>
-  <si>
-    <t>0.0010,0.9986,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0128,0.9813,0.0009,0.0011</t>
-  </si>
-  <si>
-    <t>0.0065,0.9922,0.0006,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.9997,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9998,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.8988,0.1605,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.6282,0.0168,0.1124,0.0028</t>
-  </si>
-  <si>
-    <t>0.9946,0.0000,0.0056,0.0000</t>
-  </si>
-  <si>
-    <t>0.9220,0.0074,0.0264,0.0016</t>
-  </si>
-  <si>
-    <t>0.0834,0.0030,0.8786,0.0041</t>
-  </si>
-  <si>
-    <t>0.0002,0.0778,0.0002,0.9835</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0006,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9996,0.8962,0.0000</t>
-  </si>
-  <si>
-    <t>0.0016,0.9980,0.0007,0.0000</t>
-  </si>
-  <si>
-    <t>0.7562,0.3139,0.0010,0.0000</t>
-  </si>
-  <si>
-    <t>0.8141,0.2268,0.0015,0.0000</t>
+    <t>0.9994,0.0002,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9994,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9978,0.0001,0.0012,0.0001</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9990,0.0004,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.2341,0.9710,0.0002</t>
+  </si>
+  <si>
+    <t>0.0059,0.1064,0.9278,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.0008,0.9993,0.0000</t>
+  </si>
+  <si>
+    <t>0.0006,0.0001,0.9989,0.0000</t>
+  </si>
+  <si>
+    <t>0.9989,0.0000,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.9937,0.0020,0.0005,0.0002</t>
+  </si>
+  <si>
+    <t>0.0638,0.0000,0.9618,0.0000</t>
+  </si>
+  <si>
+    <t>0.9808,0.0009,0.0090,0.0002</t>
+  </si>
+  <si>
+    <t>0.0690,0.0001,0.0006,0.9679</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0002,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0006,0.0000,0.0003,0.9993</t>
+  </si>
+  <si>
+    <t>0.0001,0.9722,0.9412,0.0000</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0017,0.9935,0.0019,0.0057</t>
+  </si>
+  <si>
+    <t>0.1538,0.8061,0.0102,0.0002</t>
+  </si>
+  <si>
+    <t>0.9994,0.0000,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.3096,0.0000,0.0019,0.6937</t>
+  </si>
+  <si>
+    <t>0.9994,0.0001,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.0007,0.0066,0.9985,0.0042</t>
+  </si>
+  <si>
+    <t>0.9946,0.0000,0.0035,0.0007</t>
+  </si>
+  <si>
+    <t>0.9914,0.0001,0.0047,0.0004</t>
+  </si>
+  <si>
+    <t>0.2291,0.6955,0.0097,0.0003</t>
+  </si>
+  <si>
+    <t>0.9992,0.0003,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9986,0.0006,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.7161,0.1363,0.0097,0.0002</t>
+  </si>
+  <si>
+    <t>0.9888,0.0159,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9980,0.0008,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9982,0.0006,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.9984,0.0010,0.0001,0.0001</t>
   </si>
   <si>
     <t>0.9998,0.0000,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9986,0.0007,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9361,0.0001,0.0579,0.0008</t>
-  </si>
-  <si>
-    <t>0.9996,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9997,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9994,0.0001,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9130,0.9348,0.0003</t>
-  </si>
-  <si>
-    <t>0.0004,0.8099,0.9642,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0020,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0035,0.0007,0.9935,0.0001</t>
-  </si>
-  <si>
-    <t>0.9357,0.0223,0.0083,0.0009</t>
-  </si>
-  <si>
-    <t>0.6146,0.0000,0.5976,0.0000</t>
-  </si>
-  <si>
-    <t>0.9976,0.0000,0.0016,0.0000</t>
-  </si>
-  <si>
-    <t>0.2921,0.0001,0.0003,0.8669</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.0000,0.0001,0.9997</t>
-  </si>
-  <si>
-    <t>0.0001,0.9915,0.8347,0.0000</t>
-  </si>
-  <si>
-    <t>0.9991,0.0001,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0008,0.9972,0.0008,0.0018</t>
-  </si>
-  <si>
-    <t>0.1361,0.8306,0.0112,0.0002</t>
-  </si>
-  <si>
-    <t>0.9990,0.0000,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.8958,0.0001,0.0040,0.0774</t>
-  </si>
-  <si>
-    <t>0.9995,0.0001,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.0034,0.9991,0.0038</t>
-  </si>
-  <si>
-    <t>0.9992,0.0000,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9414,0.0004,0.0389,0.0013</t>
-  </si>
-  <si>
-    <t>0.0185,0.9723,0.0028,0.0003</t>
-  </si>
-  <si>
-    <t>0.9972,0.0016,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9943,0.0027,0.0007,0.0001</t>
-  </si>
-  <si>
-    <t>0.3630,0.4627,0.0081,0.0001</t>
-  </si>
-  <si>
-    <t>0.9971,0.0015,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9945,0.0046,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9980,0.0007,0.0004,0.0002</t>
-  </si>
-  <si>
-    <t>0.9964,0.0023,0.0004,0.0003</t>
-  </si>
-  <si>
-    <t>0.9984,0.0008,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9990,0.0002,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9968,0.0015,0.0005,0.0002</t>
-  </si>
-  <si>
-    <t>0.9993,0.0001,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9638,0.0283,0.0001,0.0005</t>
-  </si>
-  <si>
-    <t>0.7535,0.3713,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.2079,0.8602,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.9770,0.0078,0.0060,0.0004</t>
-  </si>
-  <si>
-    <t>0.8487,0.1514,0.0033,0.0003</t>
-  </si>
-  <si>
-    <t>0.9987,0.0005,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9939,0.0074,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.8254,0.1884,0.0023,0.0005</t>
-  </si>
-  <si>
-    <t>0.0000,0.0016,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9957,0.0009,0.0014,0.0003</t>
+    <t>0.9997,0.0001,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9973,0.0016,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.9991,0.0002,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.7083,0.1584,0.0003,0.0030</t>
+  </si>
+  <si>
+    <t>0.3588,0.7360,0.0013,0.0000</t>
+  </si>
+  <si>
+    <t>0.8316,0.2804,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9895,0.0026,0.0029,0.0003</t>
+  </si>
+  <si>
+    <t>0.9067,0.0762,0.0063,0.0005</t>
+  </si>
+  <si>
+    <t>0.9979,0.0018,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9852,0.0146,0.0007,0.0003</t>
+  </si>
+  <si>
+    <t>0.0000,0.0086,1.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9958,0.0009,0.0013,0.0002</t>
+  </si>
+  <si>
+    <t>0.0005,0.0001,0.9996,0.0000</t>
+  </si>
+  <si>
+    <t>0.0009,0.0281,0.9962,0.0001</t>
+  </si>
+  <si>
+    <t>0.0744,0.0002,0.9387,0.0005</t>
+  </si>
+  <si>
+    <t>0.0002,0.3378,0.9963,0.0001</t>
   </si>
   <si>
     <t>0.0002,0.0001,0.9998,0.0000</t>
   </si>
   <si>
-    <t>0.0144,0.0017,0.9840,0.0000</t>
-  </si>
-  <si>
     <t>0.0001,0.0000,0.9999,0.0000</t>
   </si>
   <si>
-    <t>0.0002,0.1385,0.9986,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0002,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.0011,0.9988,0.0001</t>
-  </si>
-  <si>
-    <t>0.0185,0.0012,0.9778,0.0002</t>
-  </si>
-  <si>
-    <t>0.7890,0.0004,0.3193,0.0001</t>
-  </si>
-  <si>
-    <t>0.0042,0.0007,0.9936,0.0001</t>
-  </si>
-  <si>
-    <t>0.1036,0.3974,0.1305,0.0001</t>
-  </si>
-  <si>
-    <t>0.0054,0.8996,0.0635,0.0011</t>
-  </si>
-  <si>
-    <t>0.0446,0.0080,0.9477,0.0003</t>
-  </si>
-  <si>
-    <t>0.0628,0.0024,0.9111,0.0021</t>
-  </si>
-  <si>
-    <t>0.1764,0.0005,0.8603,0.0002</t>
-  </si>
-  <si>
-    <t>0.0232,0.9839,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.9990,0.0010,0.0000</t>
-  </si>
-  <si>
-    <t>0.5018,0.5612,0.0011,0.0001</t>
-  </si>
-  <si>
-    <t>0.4651,0.5708,0.0012,0.0001</t>
-  </si>
-  <si>
-    <t>0.7075,0.4096,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9916,0.0013,0.0010,0.0001</t>
-  </si>
-  <si>
-    <t>0.9822,0.0000,0.0404,0.0000</t>
-  </si>
-  <si>
-    <t>0.9897,0.0008,0.0020,0.0004</t>
-  </si>
-  <si>
-    <t>0.9927,0.0001,0.0042,0.0000</t>
-  </si>
-  <si>
-    <t>0.8843,0.0002,0.1736,0.0002</t>
-  </si>
-  <si>
-    <t>0.0002,0.0001,0.9995,0.0003</t>
-  </si>
-  <si>
-    <t>0.3457,0.0136,0.5321,0.0012</t>
-  </si>
-  <si>
-    <t>0.0019,0.0035,0.9955,0.0001</t>
-  </si>
-  <si>
-    <t>0.2576,0.0006,0.8173,0.0001</t>
-  </si>
-  <si>
-    <t>0.0049,0.0090,0.9758,0.0012</t>
-  </si>
-  <si>
-    <t>0.9992,0.0004,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9972,0.0014,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.9965,0.0023,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9982,0.0026,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9985,0.0012,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9989,0.0012,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9984,0.0012,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.0004,0.9995,0.0002</t>
-  </si>
-  <si>
-    <t>0.0877,0.8720,0.0058,0.0006</t>
-  </si>
-  <si>
-    <t>0.9498,0.0011,0.0170,0.0043</t>
-  </si>
-  <si>
-    <t>0.0052,0.0002,0.9960,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0016,0.9998,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.2640,0.9915,0.0001</t>
+    <t>0.0017,0.0000,0.9986,0.0001</t>
+  </si>
+  <si>
+    <t>0.0354,0.0016,0.9597,0.0001</t>
+  </si>
+  <si>
+    <t>0.2098,0.0012,0.8400,0.0001</t>
+  </si>
+  <si>
+    <t>0.0875,0.0039,0.8970,0.0001</t>
+  </si>
+  <si>
+    <t>0.0019,0.5349,0.7159,0.0003</t>
+  </si>
+  <si>
+    <t>0.0030,0.0751,0.9440,0.0014</t>
+  </si>
+  <si>
+    <t>0.0018,0.0026,0.9974,0.0001</t>
+  </si>
+  <si>
+    <t>0.5295,0.0009,0.4750,0.0007</t>
+  </si>
+  <si>
+    <t>0.0383,0.0007,0.9567,0.0004</t>
+  </si>
+  <si>
+    <t>0.0057,0.9929,0.0006,0.0001</t>
+  </si>
+  <si>
+    <t>0.0013,0.9980,0.0007,0.0000</t>
+  </si>
+  <si>
+    <t>0.4347,0.6601,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.9117,0.1530,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.5571,0.4854,0.0006,0.0002</t>
+  </si>
+  <si>
+    <t>0.9292,0.0120,0.0194,0.0009</t>
+  </si>
+  <si>
+    <t>0.9951,0.0000,0.0043,0.0000</t>
+  </si>
+  <si>
+    <t>0.8891,0.0078,0.0389,0.0053</t>
+  </si>
+  <si>
+    <t>0.2731,0.0024,0.7645,0.0004</t>
+  </si>
+  <si>
+    <t>0.9239,0.0007,0.0824,0.0003</t>
+  </si>
+  <si>
+    <t>0.0029,0.0003,0.9961,0.0006</t>
+  </si>
+  <si>
+    <t>0.0043,0.0018,0.9906,0.0005</t>
+  </si>
+  <si>
+    <t>0.0012,0.0030,0.9970,0.0001</t>
+  </si>
+  <si>
+    <t>0.0220,0.0004,0.9853,0.0000</t>
+  </si>
+  <si>
+    <t>0.0073,0.0018,0.9867,0.0002</t>
+  </si>
+  <si>
+    <t>0.9987,0.0008,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9987,0.0006,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9893,0.0131,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9971,0.0044,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9960,0.0043,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9976,0.0016,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9983,0.0011,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0016,0.0004,0.9985,0.0002</t>
+  </si>
+  <si>
+    <t>0.2983,0.2066,0.1812,0.0003</t>
+  </si>
+  <si>
+    <t>0.9756,0.0003,0.0069,0.0038</t>
+  </si>
+  <si>
+    <t>0.0101,0.0025,0.9879,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0007,0.9998,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.0373,0.9912,0.0013</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0027,0.0024,0.9948,0.0001</t>
   </si>
   <si>
     <t>0.0001,0.0001,0.9999,0.0000</t>
   </si>
   <si>
-    <t>0.0013,0.0006,0.9970,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0004,0.9995,0.0001</t>
-  </si>
-  <si>
-    <t>0.0129,0.0185,0.9676,0.0004</t>
-  </si>
-  <si>
-    <t>0.9823,0.0002,0.0119,0.0006</t>
-  </si>
-  <si>
-    <t>0.9495,0.0002,0.0729,0.0001</t>
-  </si>
-  <si>
-    <t>0.9913,0.0001,0.0074,0.0001</t>
-  </si>
-  <si>
-    <t>0.9982,0.0016,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9941,0.0073,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9997,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9846,0.0179,0.0009,0.0001</t>
-  </si>
-  <si>
-    <t>0.9993,0.0002,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9979,0.0023,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9959,0.0051,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0034,0.0031,0.9913,0.0003</t>
-  </si>
-  <si>
-    <t>0.0001,0.0002,0.9998,0.0001</t>
-  </si>
-  <si>
-    <t>0.0019,0.0009,0.9950,0.0004</t>
-  </si>
-  <si>
-    <t>0.0197,0.0975,0.6196,0.0018</t>
-  </si>
-  <si>
-    <t>0.0006,0.0001,0.9988,0.0001</t>
-  </si>
-  <si>
-    <t>0.9124,0.0000,0.1288,0.0003</t>
-  </si>
-  <si>
-    <t>0.0037,0.0008,0.9918,0.0008</t>
-  </si>
-  <si>
-    <t>0.0006,0.0013,0.9971,0.0018</t>
-  </si>
-  <si>
-    <t>0.9992,0.0000,0.0001,0.0004</t>
-  </si>
-  <si>
-    <t>0.1010,0.0001,0.0000,0.9719</t>
-  </si>
-  <si>
-    <t>0.0132,0.0001,0.0025,0.9892</t>
-  </si>
-  <si>
-    <t>0.9638,0.0001,0.0001,0.0281</t>
+    <t>0.0020,0.0003,0.9976,0.0000</t>
+  </si>
+  <si>
+    <t>0.0054,0.0031,0.9895,0.0004</t>
+  </si>
+  <si>
+    <t>0.9975,0.0000,0.0022,0.0000</t>
+  </si>
+  <si>
+    <t>0.9880,0.0000,0.0172,0.0000</t>
+  </si>
+  <si>
+    <t>0.9803,0.0004,0.0166,0.0001</t>
+  </si>
+  <si>
+    <t>0.9961,0.0038,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9989,0.0009,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9986,0.0019,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9835,0.0240,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.9978,0.0031,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0011,0.0076,0.9959,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.0008,0.9994,0.0000</t>
+  </si>
+  <si>
+    <t>0.0022,0.0053,0.9941,0.0003</t>
+  </si>
+  <si>
+    <t>0.0142,0.0173,0.9396,0.0006</t>
+  </si>
+  <si>
+    <t>0.0002,0.0000,0.9997,0.0000</t>
+  </si>
+  <si>
+    <t>0.1951,0.0000,0.8212,0.0007</t>
+  </si>
+  <si>
+    <t>0.0082,0.0001,0.9895,0.0002</t>
+  </si>
+  <si>
+    <t>0.0012,0.0001,0.9968,0.0004</t>
+  </si>
+  <si>
+    <t>0.9957,0.0000,0.0007,0.0026</t>
+  </si>
+  <si>
+    <t>0.2180,0.0015,0.0001,0.9343</t>
+  </si>
+  <si>
+    <t>0.0036,0.0002,0.0137,0.9921</t>
+  </si>
+  <si>
+    <t>0.0002,0.0001,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.9973,0.0001,0.0001,0.0006</t>
   </si>
 </sst>
 </file>
@@ -1890,7 +1887,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1904,7 +1901,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1918,7 +1915,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1932,7 +1929,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1946,7 +1943,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1960,7 +1957,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2030,7 +2027,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2058,7 +2055,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2072,7 +2069,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2083,10 +2080,10 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D16" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2100,7 +2097,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2114,7 +2111,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2128,7 +2125,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2142,7 +2139,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2156,7 +2153,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2170,7 +2167,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2184,7 +2181,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2195,10 +2192,10 @@
         <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D24" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2212,7 +2209,7 @@
         <v>259</v>
       </c>
       <c r="D25" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2226,7 +2223,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2240,7 +2237,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2254,7 +2251,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2268,7 +2265,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2282,7 +2279,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2296,7 +2293,7 @@
         <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2310,7 +2307,7 @@
         <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2324,7 +2321,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2338,7 +2335,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2352,7 +2349,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2366,7 +2363,7 @@
         <v>261</v>
       </c>
       <c r="D36" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2377,10 +2374,10 @@
         <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D37" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2394,7 +2391,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2408,7 +2405,7 @@
         <v>261</v>
       </c>
       <c r="D39" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2422,7 +2419,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2436,7 +2433,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2450,7 +2447,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2464,7 +2461,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2478,7 +2475,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2492,7 +2489,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2506,7 +2503,7 @@
         <v>262</v>
       </c>
       <c r="D46" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2520,7 +2517,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2534,7 +2531,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2548,7 +2545,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>309</v>
+        <v>283</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2562,7 +2559,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2576,7 +2573,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2590,7 +2587,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2604,7 +2601,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2618,7 +2615,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2632,7 +2629,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2646,7 +2643,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2660,7 +2657,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2674,7 +2671,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2688,7 +2685,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2702,7 +2699,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2716,7 +2713,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2730,7 +2727,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2744,7 +2741,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2758,7 +2755,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2772,7 +2769,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2786,7 +2783,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2800,7 +2797,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2814,7 +2811,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2828,7 +2825,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>329</v>
+        <v>283</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2842,7 +2839,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2853,10 +2850,10 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D71" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2870,7 +2867,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2884,7 +2881,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2895,10 +2892,10 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2912,7 +2909,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2926,7 +2923,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2940,7 +2937,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2954,7 +2951,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2968,7 +2965,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2982,7 +2979,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2996,7 +2993,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3010,7 +3007,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3024,7 +3021,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3038,7 +3035,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3052,7 +3049,7 @@
         <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3063,10 +3060,10 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D86" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3080,7 +3077,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3091,10 +3088,10 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D88" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3108,7 +3105,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3122,7 +3119,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3136,7 +3133,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3150,7 +3147,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3164,7 +3161,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3178,7 +3175,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3192,7 +3189,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3206,7 +3203,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3234,7 +3231,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3248,7 +3245,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>349</v>
+        <v>271</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3262,7 +3259,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>349</v>
+        <v>271</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3276,7 +3273,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>357</v>
+        <v>269</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3290,7 +3287,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3304,7 +3301,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3332,7 +3329,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3346,7 +3343,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3360,7 +3357,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3374,7 +3371,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3388,7 +3385,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3402,7 +3399,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>329</v>
+        <v>363</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3416,7 +3413,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3430,7 +3427,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3444,7 +3441,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3458,7 +3455,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3469,10 +3466,10 @@
         <v>262</v>
       </c>
       <c r="C115" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D115" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3483,10 +3480,10 @@
         <v>259</v>
       </c>
       <c r="C116" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D116" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3500,7 +3497,7 @@
         <v>259</v>
       </c>
       <c r="D117" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3514,7 +3511,7 @@
         <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3525,10 +3522,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D119" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3542,7 +3539,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3556,7 +3553,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>329</v>
+        <v>363</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3570,7 +3567,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>309</v>
+        <v>283</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3584,7 +3581,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3598,7 +3595,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3612,7 +3609,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3626,7 +3623,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3640,7 +3637,7 @@
         <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3654,7 +3651,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3668,7 +3665,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3682,7 +3679,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3696,7 +3693,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3710,7 +3707,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3724,7 +3721,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>380</v>
+        <v>269</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3738,7 +3735,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3752,7 +3749,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3763,10 +3760,10 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D136" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3777,10 +3774,10 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D137" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3794,7 +3791,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3808,7 +3805,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3822,7 +3819,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>271</v>
+        <v>388</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3836,7 +3833,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3850,7 +3847,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3864,7 +3861,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3878,7 +3875,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3892,7 +3889,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3976,7 +3973,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>356</v>
+        <v>271</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4015,7 +4012,7 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D154" t="s">
         <v>401</v>
@@ -4200,7 +4197,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>414</v>
+        <v>379</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4214,7 +4211,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4228,7 +4225,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>384</v>
+        <v>415</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4256,7 +4253,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>380</v>
+        <v>414</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4295,7 +4292,7 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D174" t="s">
         <v>419</v>
@@ -4309,7 +4306,7 @@
         <v>262</v>
       </c>
       <c r="C175" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D175" t="s">
         <v>420</v>
@@ -4354,7 +4351,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>423</v>
+        <v>269</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4368,7 +4365,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4382,7 +4379,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4396,7 +4393,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4410,7 +4407,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4424,7 +4421,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4438,7 +4435,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4452,7 +4449,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4466,7 +4463,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4480,7 +4477,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4494,7 +4491,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>314</v>
+        <v>432</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4533,7 +4530,7 @@
         <v>259</v>
       </c>
       <c r="C191" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D191" t="s">
         <v>435</v>
@@ -4561,7 +4558,7 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D193" t="s">
         <v>437</v>
@@ -4575,7 +4572,7 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D194" t="s">
         <v>438</v>
@@ -4603,7 +4600,7 @@
         <v>259</v>
       </c>
       <c r="C196" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D196" t="s">
         <v>440</v>
@@ -4673,7 +4670,7 @@
         <v>259</v>
       </c>
       <c r="C201" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D201" t="s">
         <v>445</v>
@@ -4743,7 +4740,7 @@
         <v>261</v>
       </c>
       <c r="C206" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D206" t="s">
         <v>450</v>
@@ -4942,7 +4939,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>349</v>
+        <v>414</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4967,7 +4964,7 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D222" t="s">
         <v>465</v>
@@ -5208,7 +5205,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>482</v>
+        <v>270</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5222,7 +5219,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>483</v>
+        <v>348</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5236,7 +5233,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5250,7 +5247,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5264,7 +5261,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5278,7 +5275,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5292,7 +5289,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5306,7 +5303,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5320,7 +5317,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5331,10 +5328,10 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5348,7 +5345,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5362,7 +5359,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5376,7 +5373,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5390,7 +5387,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5404,7 +5401,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5418,7 +5415,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5432,7 +5429,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>394</v>
+        <v>494</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5446,7 +5443,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
   </sheetData>
